--- a/storage/app/public/vocabs/geochemistry/1.3/geochemistry_1-3.xlsx
+++ b/storage/app/public/vocabs/geochemistry/1.3/geochemistry_1-3.xlsx
@@ -707,7 +707,7 @@
     <t>x-ray fluorescence spectrometer</t>
   </si>
   <si>
-    <t>#xrf</t>
+    <t>#xrf#(xrf)#x-ray fluorescence#x-ray fluoresence</t>
   </si>
   <si>
     <t>https://epos-msl.uu.nl/voc/geochemistry/1.3/equipment-x-ray_spectrometer-x-ray_fluorescence_spectrometer</t>
